--- a/results/3judge_composition_counts.xlsx
+++ b/results/3judge_composition_counts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9">
@@ -552,16 +552,16 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -569,26 +569,12 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>0</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" t="n">
         <v>1</v>
       </c>
     </row>
